--- a/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>YJL037W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YKL034W</t>
+          <t>YMR319C</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YBR187W</t>
+          <t>YLR332W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YMR244W</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YHR134W</t>
+          <t>YBR302C</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YJL223C</t>
+          <t>YOR119C</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YKL224C</t>
+          <t>YKR044W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YJL174W</t>
+          <t>YMR155W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YNL217W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YDL133W</t>
+          <t>YOR247W</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YDR536W</t>
+          <t>YLL043W</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YDR519W</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YNR002C</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YPL282C</t>
+          <t>YBR162C</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YHR126C</t>
+          <t>YOL101C</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YLR104W</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YKL165C</t>
+          <t>YJR054W</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YHR215W</t>
+          <t>YLR194C</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YNL322C</t>
+          <t>YIL014W</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>YNL019C</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YOR049C</t>
+          <t>YNL305C</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YDL133W</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YJR161C</t>
+          <t>YML132W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YHR132C</t>
+          <t>YOL122C</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YPL123C</t>
+          <t>YOL158C</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YLR299W</t>
+          <t>YBR205W</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YDR281C</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YOR383C</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YPL057C</t>
+          <t>YDR542W</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YCR069W</t>
+          <t>YJL178C</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YLR250W</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YGR279C</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YJL037W</t>
+          <t>YHL048W</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YDR144C</t>
+          <t>YGR254W</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>YKL096W</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YKL124W</t>
+          <t>YEL060C</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YIL140W</t>
+          <t>YMR297W</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YOL019W</t>
+          <t>YOL154W</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>YDR452W</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YOR214C</t>
+          <t>YNR072W</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YDL128W</t>
+          <t>YMR251W-A</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YHR151C</t>
+          <t>YNL275W</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YHR057C</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YHL047C</t>
+          <t>YMR058W</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YDR452W</t>
+          <t>YOL019W</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YOR010C</t>
+          <t>YPL282C</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YGL263W</t>
+          <t>YNL115C</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YGL032C</t>
+          <t>YNL012W</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YOR008C</t>
+          <t>YLR443W</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YLL025W</t>
+          <t>YDL077C</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>YPL221W</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YLR220W</t>
+          <t>YKR093W</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YPR157W</t>
+          <t>YNL176C</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YOL011W</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YML104C</t>
+          <t>YOR381W</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YLR297W</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YDL180W</t>
+          <t>YDL046W</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YDR144C</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YMR011W</t>
+          <t>YNL336W</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YNL238W</t>
+          <t>YPR026W</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YJL158C</t>
+          <t>YIL088C</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YNR072W</t>
+          <t>YIR041W</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YIL173W</t>
+          <t>YDL130W</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YIL011W</t>
+          <t>YPR194C</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YGL203C</t>
+          <t>YHR134W</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YEL065W</t>
+          <t>YHR215W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YMR221C</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YJL172W</t>
+          <t>YJL160C</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YLR396C</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YOR328W</t>
+          <t>YGR282C</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YJR103W</t>
+          <t>YKL196C</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YKL209C</t>
+          <t>YOL105C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YOR288C</t>
+          <t>YMR215W</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YKL217W</t>
+          <t>YDR382W</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>YOL132W</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YHR143W</t>
+          <t>YNL238W</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YCL001W</t>
+          <t>YDR040C</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>YPL156C</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YOR049C</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YJL219W</t>
+          <t>YCR098C</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YKR093W</t>
+          <t>YNL320W</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YOR381W</t>
+          <t>YJL097W</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YJL222W</t>
+          <t>YCR011C</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YLR110C</t>
+          <t>YJL116C</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YOL105C</t>
+          <t>YOR316C</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YKL146W</t>
+          <t>YOR034C</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YGL089C</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YBR162C</t>
+          <t>YLR461W</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YNL321W</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>YDR003W</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YJR137C</t>
+          <t>YKL165C</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>YDL128W</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YHL036W</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YCR098C</t>
+          <t>YNR076W</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YDR497C</t>
+          <t>YJL223C</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YLR037C</t>
+          <t>YKL034W</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YPR075C</t>
+          <t>YCR075C</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YDR422C</t>
+          <t>YLR361C</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YOL158C</t>
+          <t>YJL219W</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YGR197C</t>
+          <t>YOR270C</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YOR301W</t>
+          <t>YGL032C</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>YKL124W</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YML123C</t>
+          <t>YJL222W</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YLL048C</t>
+          <t>YEL065W</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YJR040W</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YBR014C</t>
+          <t>YLR300W</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YJL079C</t>
+          <t>YNR061C</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YEL060C</t>
+          <t>YML123C</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YBR205W</t>
+          <t>YHL042W</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>YNL279W</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>YJL172W</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YLR194C</t>
+          <t>YOR301W</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YML104C</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YNL101W</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YIR019C</t>
+          <t>YDR248C</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YNL065W</t>
+          <t>YNR055C</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YLR332W</t>
+          <t>YOR010C</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YHR143W</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YML047C</t>
+          <t>YGL263W</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YIL099W</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YPL053C</t>
+          <t>YLR413W</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YMR319C</t>
+          <t>YOL103W</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YHR174W</t>
+          <t>YPR037C</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YHR057C</t>
+          <t>YIL011W</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YJR004C</t>
+          <t>YNL058C</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YBL039C</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YCR101C</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YGL027C</t>
+          <t>YBL042C</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YKR044W</t>
+          <t>YCR069W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YPR075C</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YJL079C</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YBR290W</t>
+          <t>YBL017C</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YKR013W</t>
+          <t>YIL089W</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YOR099W</t>
+          <t>YIL067C</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YNL275W</t>
+          <t>YNL318C</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YER060W-A</t>
+          <t>YLR286C</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YCL057W</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YGR209C</t>
+          <t>YNR066C</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YBR040W</t>
+          <t>YPL053C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YCR011C</t>
+          <t>YIL140W</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YJL160C</t>
+          <t>YJR161C</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YBL042C</t>
+          <t>YDL180W</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YIR041W</t>
+          <t>YNL322C</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YLR300W</t>
+          <t>YML001W</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YOR034C</t>
+          <t>YPL123C</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YBL017C</t>
+          <t>YPL154C</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YNR028W</t>
+          <t>YJR004C</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YOL103W</t>
+          <t>YHR151C</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YGR282C</t>
+          <t>YOR009W</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YBR036C</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YLR443W</t>
+          <t>YPL163C</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YPL265W</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YPL234C</t>
+          <t>YPL265W</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YML066C</t>
+          <t>YDR497C</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YOL002C</t>
+          <t>YFL062W</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YOL101C</t>
+          <t>YHR173C</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YDR040C</t>
+          <t>YJR137C</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YNL279W</t>
+          <t>YNL327W</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YCR075C</t>
+          <t>YOL138C</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YER119C</t>
+          <t>YLR001C</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YNL321W</t>
+          <t>YGL203C</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YPL221W</t>
+          <t>YCL001W</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YJL174W</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YJL051W</t>
+          <t>YJR001W</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YML001W</t>
+          <t>YDR262W</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YMR215W</t>
+          <t>YOR214C</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YLR343W</t>
+          <t>YGR260W</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YNR076W</t>
+          <t>YCR007C</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YOR190W</t>
+          <t>YMR011W</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>YJL132W</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YOR270C</t>
+          <t>YKL220C</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YOL011W</t>
+          <t>YIL158W</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YNL012W</t>
+          <t>YDR422C</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YPL163C</t>
+          <t>YHR174W</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YNL015W</t>
+          <t>YHL040C</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YBR161W</t>
+          <t>YER119C</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YJR160C</t>
+          <t>YHR132C</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YOL132W</t>
+          <t>YPL057C</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YBR286W</t>
+          <t>YPL176C</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YER011W</t>
+          <t>YGL186C</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YNR028W</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YNL327W</t>
+          <t>YOR087W</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YLR250W</t>
+          <t>YLR042C</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YLR396C</t>
+          <t>YIR019C</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YJR152W</t>
+          <t>YFL011W</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YBR199W</t>
+          <t>YER123W</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YHL036W</t>
+          <t>YDR415C</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YOL138C</t>
+          <t>YHR202W</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YGR279C</t>
+          <t>YLR046C</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YPR037C</t>
+          <t>YML012W</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YGR209C</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YMR243C</t>
+          <t>YJL059W</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YER011W</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YIR028W</t>
+          <t>YBR014C</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YPL156C</t>
+          <t>YHL008C</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YDL046W</t>
+          <t>YDL049C</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>YKL096W</t>
+          <t>YHR126C</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YDR519W</t>
+          <t>YJL158C</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YKL217W</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YDL049C</t>
+          <t>YLL048C</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YOR247W</t>
+          <t>YDL010W</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YHL048W</t>
+          <t>YBR139W</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YOL084W</t>
+          <t>YGR295C</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YOL122C</t>
+          <t>YLR213C</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YOR009W</t>
+          <t>YLR220W</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YGR223C</t>
+          <t>YOL084W</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YBR036C</t>
+          <t>YOR008C</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YFL020C</t>
+          <t>YOR099W</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YLR110C</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YNL326C</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YMR058W</t>
+          <t>YHL047C</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YMR251W-A</t>
+          <t>YER060W-A</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YJL051W</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YOL161C</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>YOR292C</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YNL298W</t>
+          <t>YBR021W</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YBR040W</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YKR013W</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YNL283C</t>
+          <t>YGR223C</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YBL039C</t>
+          <t>YIL166C</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YGL186C</t>
+          <t>YIL162W</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>YOL154W</t>
+          <t>YKL224C</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>YPR026W</t>
+          <t>YKL209C</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YDR438W</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>YDR542W</t>
+          <t>YGR055W</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>YGR055W</t>
+          <t>YNL015W</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YER123W</t>
+          <t>YIL173W</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YGL027C</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>YLR361C</t>
+          <t>YNL283C</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>YPR194C</t>
+          <t>YPR157W</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YJR040W</t>
+          <t>YJR103W</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YCR007C</t>
+          <t>YPL234C</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YIL166C</t>
+          <t>YOR288C</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YLR042C</t>
+          <t>YFL040W</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>YLR104W</t>
+          <t>YJL151C</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YKL103C</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YNL101W</t>
+          <t>YLR343W</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YBR021W</t>
+          <t>YML066C</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YGR254W</t>
+          <t>YDR536W</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YNL129W</t>
+          <t>YOL002C</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>YCR028C</t>
+          <t>YNL129W</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>YIL158W</t>
+          <t>YNL298W</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>YOL161C</t>
+          <t>YBR290W</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>YDR382W</t>
+          <t>YLR299W</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YMR243C</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>YOR383C</t>
+          <t>YBR199W</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YLR213C</t>
+          <t>YDL211C</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YLR413W</t>
+          <t>YFL020C</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YKL220C</t>
+          <t>YKL146W</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YDL077C</t>
+          <t>YIR028W</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YDL010W</t>
+          <t>YOL007C</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YBR139W</t>
+          <t>YJR152W</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YNR002C</t>
+          <t>YGR125W</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>YBR302C</t>
+          <t>YOR328W</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YBR161W</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>YDL248W</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YLR461W</t>
+          <t>YBR187W</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>YLR043C</t>
+          <t>YGR197C</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>YKL103C</t>
+          <t>YML047C</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YJR054W</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YLR286C</t>
+          <t>YLL025W</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>YML012W</t>
+          <t>YOR382W</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>YOR382W</t>
+          <t>YLR043C</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>YNL065W</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>YLL051C</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>YDL130W</t>
+          <t>YOR190W</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>YHL040C</t>
+          <t>YCR028C</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YIL014W</t>
+          <t>YLR037C</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YBR286W</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YGL089C</t>
+          <t>YJR160C</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YJL037W</t>
+          <t>YDR438W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YMR319C</t>
+          <t>YJL037W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YLR332W</t>
+          <t>YJL223C</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>YER119C</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YBR302C</t>
+          <t>YJL219W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YLR042C</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YKR044W</t>
+          <t>YLR343W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YLR037C</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YNL327W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YOR247W</t>
+          <t>YIL158W</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YMR155W</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YDR519W</t>
+          <t>YGL263W</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YNR002C</t>
+          <t>YLL043W</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YBR162C</t>
+          <t>YDL128W</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YOL101C</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YLR104W</t>
+          <t>YJL222W</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YJR054W</t>
+          <t>YDL248W</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YLR194C</t>
+          <t>YDR497C</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YIL014W</t>
+          <t>YOL158C</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>YNL279W</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YLR194C</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YDL133W</t>
+          <t>YLR361C</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YJL172W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YOL122C</t>
+          <t>YMR243C</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YOL158C</t>
+          <t>YMR011W</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YBR205W</t>
+          <t>YNR061C</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YMR244W</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YOR192C</t>
+          <t>YNL129W</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YOR383C</t>
+          <t>YNL217W</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YDR542W</t>
+          <t>YOL011W</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YBR286W</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YLR250W</t>
+          <t>YCR011C</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YGR279C</t>
+          <t>YIL162W</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YHL048W</t>
+          <t>YDL010W</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YGR254W</t>
+          <t>YLR396C</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YKL096W</t>
+          <t>YLR043C</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YEL060C</t>
+          <t>YHR057C</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YDL180W</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YOL154W</t>
+          <t>YLR110C</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YDR452W</t>
+          <t>YGR295C</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YNR072W</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YMR251W-A</t>
+          <t>YPL053C</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YNL275W</t>
+          <t>YOL105C</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YHR057C</t>
+          <t>YJL079C</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>YJR160C</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YMR058W</t>
+          <t>YGR197C</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YOL019W</t>
+          <t>YNL176C</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YPL282C</t>
+          <t>YDR040C</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>YNL320W</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YNL012W</t>
+          <t>YCL057W</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YLR443W</t>
+          <t>YGL203C</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YDL077C</t>
+          <t>YER011W</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YPL221W</t>
+          <t>YPL123C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YKR093W</t>
+          <t>YNL101W</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YCR007C</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YOL011W</t>
+          <t>YHR202W</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YOR381W</t>
+          <t>YGR254W</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>YKR044W</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YDL046W</t>
+          <t>YHL040C</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YDR144C</t>
+          <t>YBR139W</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YNL305C</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YPR026W</t>
+          <t>YLL051C</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YFL062W</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YIR041W</t>
+          <t>YFL020C</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YDL130W</t>
+          <t>YOR192C</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YPR194C</t>
+          <t>YJR137C</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YHR134W</t>
+          <t>YHL042W</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YHR215W</t>
+          <t>YPR157W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YMR251W-A</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YJL160C</t>
+          <t>YLR104W</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YLR396C</t>
+          <t>YBR040W</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YGR282C</t>
+          <t>YIL011W</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YOR288C</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YOL105C</t>
+          <t>YHL047C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YMR215W</t>
+          <t>YDR382W</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YDR382W</t>
+          <t>YBR161W</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YOL132W</t>
+          <t>YPL156C</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YNL238W</t>
+          <t>YBL039C</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YDR040C</t>
+          <t>YDR536W</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YPL156C</t>
+          <t>YHR143W</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YOR049C</t>
+          <t>YIL140W</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YCR098C</t>
+          <t>YOR009W</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YOR247W</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YMR058W</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YCR011C</t>
+          <t>YLR413W</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YCR075C</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YOL161C</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YOR034C</t>
+          <t>YGL186C</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YGL089C</t>
+          <t>YOR087W</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YLR461W</t>
+          <t>YNR072W</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YNL321W</t>
+          <t>YDL133W</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YHL036W</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YKL165C</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YDL128W</t>
+          <t>YKL096W</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YHL036W</t>
+          <t>YPR026W</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YOR382W</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YNR076W</t>
+          <t>YNL058C</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YJL223C</t>
+          <t>YOR214C</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YKL034W</t>
+          <t>YLR213C</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YCR075C</t>
+          <t>YNL322C</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YLR361C</t>
+          <t>YGL027C</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YJL219W</t>
+          <t>YPL176C</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YPR037C</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YDR055W</t>
+          <t>YDR542W</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YOR270C</t>
+          <t>YOR190W</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YGL032C</t>
+          <t>YFL040W</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YKL124W</t>
+          <t>YPR075C</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YJL222W</t>
+          <t>YBR162C</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YEL065W</t>
+          <t>YGR279C</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YJR040W</t>
+          <t>YOR381W</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YLR300W</t>
+          <t>YHR134W</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YBL017C</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YML123C</t>
+          <t>YKR093W</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>YJR040W</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YNL279W</t>
+          <t>YDR055W</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YJL172W</t>
+          <t>YHR174W</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YOR301W</t>
+          <t>YLR300W</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YML104C</t>
+          <t>YOR049C</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YNL101W</t>
+          <t>YOR292C</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>YNL336W</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YDL211C</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YOR010C</t>
+          <t>YLR443W</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YHR143W</t>
+          <t>YGR223C</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YGL263W</t>
+          <t>YHR151C</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YFL011W</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YLR413W</t>
+          <t>YML047C</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YOL103W</t>
+          <t>YER123W</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YPR037C</t>
+          <t>YOL002C</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YIL011W</t>
+          <t>YIL067C</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YCR101C</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YBL039C</t>
+          <t>YLL048C</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>YGL032C</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YBL042C</t>
+          <t>YNL326C</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YCR069W</t>
+          <t>YML132W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YPR075C</t>
+          <t>YNR028W</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YJL079C</t>
+          <t>YJR103W</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YBL017C</t>
+          <t>YNL238W</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>YJR152W</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>YNR055C</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YDR452W</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YLR286C</t>
+          <t>YHR173C</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YJL178C</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YKL146W</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YPL053C</t>
+          <t>YKL209C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YIL140W</t>
+          <t>YIL088C</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YJR161C</t>
+          <t>YLR001C</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YDL180W</t>
+          <t>YMR221C</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YNL322C</t>
+          <t>YOR316C</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YML001W</t>
+          <t>YDR281C</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YPL123C</t>
+          <t>YHR132C</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YNL275W</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YJR004C</t>
+          <t>YIL089W</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YHR151C</t>
+          <t>YOL084W</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YOR009W</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YBR036C</t>
+          <t>YJL151C</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YPL163C</t>
+          <t>YLR299W</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YJL160C</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YPL265W</t>
+          <t>YLR461W</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YDR497C</t>
+          <t>YLR220W</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YNL015W</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>YDR144C</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YJR137C</t>
+          <t>YEL065W</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YNL327W</t>
+          <t>YKL196C</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YOL138C</t>
+          <t>YBR302C</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YKL124W</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YGL203C</t>
+          <t>YKL165C</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YCL001W</t>
+          <t>YBR036C</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YJL174W</t>
+          <t>YJR161C</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YOR034C</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YOR270C</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YOR214C</t>
+          <t>YPL234C</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YDL046W</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YCR007C</t>
+          <t>YOL101C</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YMR011W</t>
+          <t>YOR099W</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>YJL116C</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YKL220C</t>
+          <t>YNL065W</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YIL158W</t>
+          <t>YOR119C</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YDR422C</t>
+          <t>YCR028C</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YHR174W</t>
+          <t>YCR098C</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YHL040C</t>
+          <t>YCL001W</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YER119C</t>
+          <t>YER060W-A</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YHR132C</t>
+          <t>YDR415C</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YPL057C</t>
+          <t>YLR250W</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YOL007C</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YGL186C</t>
+          <t>YPL057C</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YNR028W</t>
+          <t>YKL224C</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YDL130W</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YLR042C</t>
+          <t>YHL008C</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YIR019C</t>
+          <t>YBR290W</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YJL051W</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YER123W</t>
+          <t>YNR066C</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>YNR076W</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YGR055W</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>YML066C</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YML012W</t>
+          <t>YGR260W</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YGR209C</t>
+          <t>YOL132W</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YDL077C</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YER011W</t>
+          <t>YNL115C</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YBR014C</t>
+          <t>YDR262W</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>YPR194C</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YDL049C</t>
+          <t>YGR209C</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YJL158C</t>
+          <t>YOR383C</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YKL217W</t>
+          <t>YBR014C</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YLL048C</t>
+          <t>YGR125W</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YDL010W</t>
+          <t>YPL154C</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YBR139W</t>
+          <t>YJR004C</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YOL019W</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YLR213C</t>
+          <t>YIL014W</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YLR220W</t>
+          <t>YNL019C</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YOL084W</t>
+          <t>YPL221W</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YOR008C</t>
+          <t>YBL042C</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YOR099W</t>
+          <t>YDR519W</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YLR110C</t>
+          <t>YMR319C</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YOL122C</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YHL047C</t>
+          <t>YLR046C</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YER060W-A</t>
+          <t>YDR248C</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YJL051W</t>
+          <t>YNR002C</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>YOL161C</t>
+          <t>YPL265W</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YML104C</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YBR021W</t>
+          <t>YIL099W</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YBR040W</t>
+          <t>YIL166C</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YKR013W</t>
+          <t>YML123C</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YGR223C</t>
+          <t>YJL059W</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YIL166C</t>
+          <t>YIR019C</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YML012W</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>YKL224C</t>
+          <t>YLR286C</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>YKL209C</t>
+          <t>YML001W</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YNL318C</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>YGR055W</t>
+          <t>YJL132W</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>YNL015W</t>
+          <t>YDR422C</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YIL173W</t>
+          <t>YOR010C</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>YGL027C</t>
+          <t>YBR187W</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>YNL283C</t>
+          <t>YOR301W</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>YPR157W</t>
+          <t>YIL173W</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YJR103W</t>
+          <t>YHL048W</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YPL234C</t>
+          <t>YOR328W</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YOR288C</t>
+          <t>YGR282C</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>YKR013W</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YJR054W</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YKL103C</t>
+          <t>YIR028W</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YLR343W</t>
+          <t>YJL174W</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YML066C</t>
+          <t>YOL154W</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YDR536W</t>
+          <t>YNL012W</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YOL002C</t>
+          <t>YEL060C</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>YNL129W</t>
+          <t>YLL025W</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>YNL298W</t>
+          <t>YOL103W</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>YBR290W</t>
+          <t>YDR003W</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>YLR299W</t>
+          <t>YLR332W</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YMR243C</t>
+          <t>YBR021W</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>YBR199W</t>
+          <t>YKL220C</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>YKL103C</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YFL020C</t>
+          <t>YJL158C</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YKL146W</t>
+          <t>YKL217W</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YIR028W</t>
+          <t>YIR041W</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YJR001W</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YJR152W</t>
+          <t>YOR008C</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YPL282C</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>YOR328W</t>
+          <t>YMR297W</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>YBR161W</t>
+          <t>YGL089C</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YBR199W</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YBR187W</t>
+          <t>YOL138C</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>YGR197C</t>
+          <t>YKL034W</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>YML047C</t>
+          <t>YLR297W</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YMR215W</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YLL025W</t>
+          <t>YNL321W</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>YOR382W</t>
+          <t>YHR215W</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>YLR043C</t>
+          <t>YPL163C</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>YNL065W</t>
+          <t>YNL283C</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YBR205W</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>YOR190W</t>
+          <t>YDL049C</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>YCR028C</t>
+          <t>YNL298W</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YLR037C</t>
+          <t>YCR069W</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>YBR286W</t>
+          <t>YJL097W</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YJR160C</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YHR151C</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YJL037W</t>
+          <t>YJL116C</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YJL223C</t>
+          <t>YDL049C</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YER119C</t>
+          <t>YBR187W</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YJL219W</t>
+          <t>YGR260W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YLR042C</t>
+          <t>YNL129W</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YLR343W</t>
+          <t>YLR286C</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YLR037C</t>
+          <t>YPL163C</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YNL327W</t>
+          <t>YOR214C</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YIL158W</t>
+          <t>YBR290W</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YJL172W</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YGL263W</t>
+          <t>YMR243C</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YFL020C</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YDL128W</t>
+          <t>YMR058W</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YKR013W</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YJL222W</t>
+          <t>YCR098C</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YNL279W</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YDR497C</t>
+          <t>YOR301W</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YOL158C</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YNL279W</t>
+          <t>YLR220W</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YLR194C</t>
+          <t>YNL176C</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YLR361C</t>
+          <t>YJL097W</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YJL172W</t>
+          <t>YJL037W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YMR243C</t>
+          <t>YCR028C</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YMR011W</t>
+          <t>YOL132W</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YBR286W</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>YKL220C</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YNL129W</t>
+          <t>YLR361C</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YDL180W</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YOL011W</t>
+          <t>YML066C</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YBR286W</t>
+          <t>YDL130W</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YCR011C</t>
+          <t>YLR343W</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YPL057C</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YDL010W</t>
+          <t>YEL060C</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YLR396C</t>
+          <t>YER011W</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YLR043C</t>
+          <t>YOR270C</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YHR057C</t>
+          <t>YDR382W</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YDL180W</t>
+          <t>YDR519W</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YLR110C</t>
+          <t>YNR028W</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YKL146W</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YOL084W</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YPL053C</t>
+          <t>YCR011C</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YOL105C</t>
+          <t>YJL051W</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YJL079C</t>
+          <t>YBR036C</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YJR160C</t>
+          <t>YER060W-A</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YGR197C</t>
+          <t>YIL089W</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YML012W</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YML123C</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YDR040C</t>
+          <t>YBR199W</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YBR021W</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YKR044W</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YGL203C</t>
+          <t>YOR288C</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YER011W</t>
+          <t>YMR221C</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YPL123C</t>
+          <t>YNR055C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YNL101W</t>
+          <t>YKL224C</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YCR007C</t>
+          <t>YCL001W</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YGL203C</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YGR254W</t>
+          <t>YFL040W</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YKR044W</t>
+          <t>YLR110C</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YHL040C</t>
+          <t>YMR244W</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YBR139W</t>
+          <t>YPL282C</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YGL263W</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YBR040W</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YJR001W</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YFL020C</t>
+          <t>YLR194C</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YOR192C</t>
+          <t>YML104C</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YJR137C</t>
+          <t>YNL318C</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>YHR057C</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YPR157W</t>
+          <t>YJL160C</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YMR251W-A</t>
+          <t>YNL326C</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YLR104W</t>
+          <t>YDL211C</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YBR040W</t>
+          <t>YOR099W</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YIL011W</t>
+          <t>YDR055W</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YOR288C</t>
+          <t>YKL217W</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YHL047C</t>
+          <t>YGL186C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YDR382W</t>
+          <t>YIL011W</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YBR161W</t>
+          <t>YLR037C</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YPL156C</t>
+          <t>YLR046C</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YBL039C</t>
+          <t>YLR413W</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YDR536W</t>
+          <t>YJL174W</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YHR143W</t>
+          <t>YKL196C</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YIL140W</t>
+          <t>YKR093W</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YOR009W</t>
+          <t>YBR205W</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YOR247W</t>
+          <t>YJL059W</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YMR058W</t>
+          <t>YLR001C</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YLR413W</t>
+          <t>YOR009W</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YCR075C</t>
+          <t>YOR049C</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YOL161C</t>
+          <t>YDR248C</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YGL186C</t>
+          <t>YJR160C</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YOL158C</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YNR072W</t>
+          <t>YOL007C</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YDL133W</t>
+          <t>YJL223C</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YHL036W</t>
+          <t>YIL162W</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YLR443W</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YKL096W</t>
+          <t>YOL002C</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YPR026W</t>
+          <t>YCR075C</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YOR382W</t>
+          <t>YDR040C</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YIL173W</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YOR214C</t>
+          <t>YOR119C</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YLR213C</t>
+          <t>YOR328W</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YNL322C</t>
+          <t>YNL305C</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YGL027C</t>
+          <t>YPR026W</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YLR297W</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YPR037C</t>
+          <t>YER123W</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YDR542W</t>
+          <t>YIL158W</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YOR190W</t>
+          <t>YKL034W</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>YML001W</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YPR075C</t>
+          <t>YHR215W</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YBR162C</t>
+          <t>YLR250W</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YGR279C</t>
+          <t>YJL079C</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YOR381W</t>
+          <t>YER119C</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YHR134W</t>
+          <t>YHR132C</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YBL017C</t>
+          <t>YHR174W</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YKR093W</t>
+          <t>YNL115C</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YJR040W</t>
+          <t>YNL327W</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YDR055W</t>
+          <t>YHR126C</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YHR174W</t>
+          <t>YNR002C</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YLR300W</t>
+          <t>YLR332W</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YOR049C</t>
+          <t>YGL027C</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YFL011W</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YBR139W</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>YOR382W</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YLR443W</t>
+          <t>YML047C</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YGR223C</t>
+          <t>YOL103W</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YHR151C</t>
+          <t>YOR316C</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YLR461W</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YML047C</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YER123W</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YOL002C</t>
+          <t>YGR254W</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>YJR004C</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>YDR452W</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YLL048C</t>
+          <t>YCR007C</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YGL032C</t>
+          <t>YLR104W</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YJR040W</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YOL011W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YNR028W</t>
+          <t>YGR125W</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YJR103W</t>
+          <t>YOL138C</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YNL238W</t>
+          <t>YOR008C</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YJR152W</t>
+          <t>YOR087W</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YPL154C</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YDR452W</t>
+          <t>YDR422C</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>YPL053C</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YOR247W</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YKL146W</t>
+          <t>YDL010W</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YKL209C</t>
+          <t>YNL275W</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YKL124W</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YGL089C</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YPL123C</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YHL040C</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YCR101C</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YHR132C</t>
+          <t>YDL133W</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YNL275W</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>YKL165C</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YOL084W</t>
+          <t>YLL043W</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>YBL017C</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YJR137C</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YLR299W</t>
+          <t>YIL166C</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YJL160C</t>
+          <t>YLR042C</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YLR461W</t>
+          <t>YDR536W</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YLR220W</t>
+          <t>YNL019C</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YNL015W</t>
+          <t>YOR383C</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YDR144C</t>
+          <t>YBR161W</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YDR415C</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YBR302C</t>
+          <t>YPR075C</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YKL124W</t>
+          <t>YJR152W</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YKL165C</t>
+          <t>YHL008C</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YBR036C</t>
+          <t>YJR103W</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YJR161C</t>
+          <t>YNL101W</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YOR034C</t>
+          <t>YNL217W</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YOR270C</t>
+          <t>YMR215W</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YPL234C</t>
+          <t>YMR297W</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YDL046W</t>
+          <t>YJL222W</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YOL101C</t>
+          <t>YKL209C</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YOR099W</t>
+          <t>YNL298W</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YHL047C</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YNL065W</t>
+          <t>YOR292C</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YDR262W</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YCR028C</t>
+          <t>YNL321W</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YCR098C</t>
+          <t>YLR043C</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YCL001W</t>
+          <t>YLR299W</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YER060W-A</t>
+          <t>YKL103C</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>YLL025W</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YLR250W</t>
+          <t>YJL219W</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YHL036W</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YPL057C</t>
+          <t>YIL014W</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YKL224C</t>
+          <t>YDR438W</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YDL130W</t>
+          <t>YDL046W</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>YHR134W</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YBR290W</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YJL051W</t>
+          <t>YNR066C</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YOL105C</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YNR076W</t>
+          <t>YPL156C</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YGR055W</t>
+          <t>YPR157W</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YML066C</t>
+          <t>YNL058C</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YOL122C</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YOL132W</t>
+          <t>YJL132W</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YDL077C</t>
+          <t>YGR209C</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>YDR281C</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YGR295C</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YPR194C</t>
+          <t>YHR143W</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YGR209C</t>
+          <t>YNL320W</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>YHR126C</t>
+          <t>YFL062W</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YOR383C</t>
+          <t>YOL101C</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YBR014C</t>
+          <t>YMR319C</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YOR192C</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YPL234C</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YJR004C</t>
+          <t>YPL265W</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YOL019W</t>
+          <t>YOR381W</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YIL014W</t>
+          <t>YPR037C</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>YIR041W</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YPL221W</t>
+          <t>YBR162C</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YBL042C</t>
+          <t>YOL161C</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YDR519W</t>
+          <t>YNL336W</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YMR319C</t>
+          <t>YLR300W</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YOL122C</t>
+          <t>YMR011W</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>YMR251W-A</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>YMR155W</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YNR002C</t>
+          <t>YBL039C</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>YPL265W</t>
+          <t>YHR202W</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YML104C</t>
+          <t>YIL140W</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YJL178C</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YIL166C</t>
+          <t>YOR034C</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YML123C</t>
+          <t>YLL051C</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YOL019W</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YIR019C</t>
+          <t>YDR003W</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YML012W</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>YLR286C</t>
+          <t>YNR072W</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>YML001W</t>
+          <t>YNR076W</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YDR144C</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>YGR279C</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>YDR422C</t>
+          <t>YLL048C</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>YBR187W</t>
+          <t>YNR061C</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>YOR301W</t>
+          <t>YNL283C</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>YIL173W</t>
+          <t>YPL176C</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YHL048W</t>
+          <t>YGR223C</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YOR328W</t>
+          <t>YNL238W</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YGR282C</t>
+          <t>YGR055W</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YKR013W</t>
+          <t>YNL015W</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>YJR054W</t>
+          <t>YKL096W</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YIR028W</t>
+          <t>YJR054W</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YJL174W</t>
+          <t>YDR542W</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YOL154W</t>
+          <t>YIR019C</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YNL012W</t>
+          <t>YJL151C</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YEL060C</t>
+          <t>YDR497C</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>YLL025W</t>
+          <t>YIL067C</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>YOL103W</t>
+          <t>YBR014C</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YIL088C</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>YLR332W</t>
+          <t>YIL099W</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YBR021W</t>
+          <t>YLR396C</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>YKL220C</t>
+          <t>YOL154W</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YKL103C</t>
+          <t>YPR194C</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YJL158C</t>
+          <t>YNL012W</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YKL217W</t>
+          <t>YDL077C</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YIR041W</t>
+          <t>YDL128W</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YHL042W</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YOR008C</t>
+          <t>YCR069W</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YPL282C</t>
+          <t>YGR282C</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YGR197C</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>YGL089C</t>
+          <t>YHR173C</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>YBR199W</t>
+          <t>YIR028W</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YOL138C</t>
+          <t>YJL158C</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>YKL034W</t>
+          <t>YHL048W</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>YML132W</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YMR215W</t>
+          <t>YDL248W</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YNL321W</t>
+          <t>YLR213C</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>YHR215W</t>
+          <t>YNL065W</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>YPL163C</t>
+          <t>YGL032C</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>YNL283C</t>
+          <t>YBR302C</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>YBR205W</t>
+          <t>YNL322C</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>YDL049C</t>
+          <t>YPL221W</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>YNL298W</t>
+          <t>YOR190W</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YCR069W</t>
+          <t>YCL057W</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YBL042C</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YJR161C</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YHR151C</t>
+          <t>YFL062W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YNL336W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YDL049C</t>
+          <t>YNR076W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YBR187W</t>
+          <t>YPL156C</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YDR497C</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YNL129W</t>
+          <t>YOR247W</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YLR286C</t>
+          <t>YDR536W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YPL163C</t>
+          <t>YOL084W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YOR214C</t>
+          <t>YGL027C</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YBR290W</t>
+          <t>YIL158W</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YJL172W</t>
+          <t>YPR037C</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YMR243C</t>
+          <t>YPL234C</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YFL020C</t>
+          <t>YJR004C</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YMR058W</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YKR013W</t>
+          <t>YJR161C</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YCR098C</t>
+          <t>YOL007C</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YOR301W</t>
+          <t>YJL151C</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YKL124W</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YLR220W</t>
+          <t>YCL057W</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YHR173C</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YHL040C</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YJL037W</t>
+          <t>YDR040C</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YCR028C</t>
+          <t>YLR046C</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YOL132W</t>
+          <t>YOL103W</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YBR286W</t>
+          <t>YOR383C</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YKL220C</t>
+          <t>YDL046W</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YLR361C</t>
+          <t>YHR174W</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YDL180W</t>
+          <t>YIL162W</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YML066C</t>
+          <t>YDL211C</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YDL130W</t>
+          <t>YIL067C</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YLR343W</t>
+          <t>YKL220C</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YPL057C</t>
+          <t>YGR223C</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YEL060C</t>
+          <t>YML123C</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YER011W</t>
+          <t>YHL042W</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YOR270C</t>
+          <t>YNL322C</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YDR382W</t>
+          <t>YOR192C</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YDR519W</t>
+          <t>YJR137C</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YNR028W</t>
+          <t>YGR197C</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YKL146W</t>
+          <t>YGL089C</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YOL084W</t>
+          <t>YKL096W</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YCR011C</t>
+          <t>YGR279C</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YJL051W</t>
+          <t>YOR214C</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YBR036C</t>
+          <t>YPL154C</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YER060W-A</t>
+          <t>YMR297W</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>YKL034W</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YML012W</t>
+          <t>YOR087W</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YML123C</t>
+          <t>YPL282C</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YBR199W</t>
+          <t>YNR028W</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YBR021W</t>
+          <t>YHR202W</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YKR044W</t>
+          <t>YJL051W</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YOR288C</t>
+          <t>YBR286W</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YIL166C</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YCR028C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YKL224C</t>
+          <t>YMR244W</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YCL001W</t>
+          <t>YOR119C</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YGL203C</t>
+          <t>YMR221C</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>YOR034C</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YLR110C</t>
+          <t>YHL047C</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>YHR151C</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YPL282C</t>
+          <t>YPL265W</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YGL263W</t>
+          <t>YIL088C</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YBR040W</t>
+          <t>YGL186C</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YLR250W</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YLR194C</t>
+          <t>YOR190W</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YML104C</t>
+          <t>YDL049C</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YOL158C</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YHR057C</t>
+          <t>YGR055W</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YJL160C</t>
+          <t>YLL025W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>YGR260W</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YOR099W</t>
+          <t>YLR104W</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YDR055W</t>
+          <t>YDR262W</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YKL217W</t>
+          <t>YOR316C</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YGL186C</t>
+          <t>YLR286C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YIL011W</t>
+          <t>YJL132W</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YLR037C</t>
+          <t>YPR075C</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YLR413W</t>
+          <t>YLR361C</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YJL174W</t>
+          <t>YML047C</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YOL019W</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YKR093W</t>
+          <t>YJL160C</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YBR205W</t>
+          <t>YPR026W</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YFL020C</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YJL223C</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YOR009W</t>
+          <t>YKL146W</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YOR049C</t>
+          <t>YBR036C</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>YNL327W</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YJR160C</t>
+          <t>YGR282C</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YOL158C</t>
+          <t>YKL209C</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YLR213C</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YJL223C</t>
+          <t>YML104C</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YBL017C</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YLR443W</t>
+          <t>YPL057C</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YOL002C</t>
+          <t>YNL305C</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YCR075C</t>
+          <t>YOL138C</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YDR040C</t>
+          <t>YMR251W-A</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YIL173W</t>
+          <t>YOR292C</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YML001W</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YOR328W</t>
+          <t>YDL077C</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YEL060C</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YPR026W</t>
+          <t>YGL032C</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>YLR343W</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YER123W</t>
+          <t>YBR187W</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YIL158W</t>
+          <t>YLR001C</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YKL034W</t>
+          <t>YJR103W</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YML001W</t>
+          <t>YKL224C</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YHR215W</t>
+          <t>YMR215W</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YLR250W</t>
+          <t>YCR101C</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YJL079C</t>
+          <t>YLR220W</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YER119C</t>
+          <t>YNR072W</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YHR132C</t>
+          <t>YJR040W</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YHR174W</t>
+          <t>YBR040W</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>YPL053C</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YNL327W</t>
+          <t>YBR302C</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YHR126C</t>
+          <t>YNL238W</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YNR002C</t>
+          <t>YLR461W</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YLR332W</t>
+          <t>YNL326C</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YGL027C</t>
+          <t>YGL203C</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YDL128W</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YBR139W</t>
+          <t>YER123W</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YOR382W</t>
+          <t>YOR009W</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YML047C</t>
+          <t>YLR413W</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YOL103W</t>
+          <t>YKL217W</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YLL043W</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YLR461W</t>
+          <t>YPR157W</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YDR144C</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YLR194C</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YGR254W</t>
+          <t>YJR160C</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YJR004C</t>
+          <t>YLR037C</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YDR452W</t>
+          <t>YNL065W</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YCR007C</t>
+          <t>YLR332W</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YLR104W</t>
+          <t>YCR098C</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YJR040W</t>
+          <t>YML012W</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YOL011W</t>
+          <t>YNL321W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YCL001W</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YOL138C</t>
+          <t>YJR054W</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YOR008C</t>
+          <t>YLR297W</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YDL133W</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YNL275W</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YDR422C</t>
+          <t>YLR396C</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YPL053C</t>
+          <t>YKL103C</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YOR247W</t>
+          <t>YGL263W</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YDL010W</t>
+          <t>YKL196C</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YNL275W</t>
+          <t>YJL158C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YKL124W</t>
+          <t>YOL105C</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YGL089C</t>
+          <t>YJL116C</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YPL123C</t>
+          <t>YOL122C</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YHL040C</t>
+          <t>YKR013W</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>YKR093W</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YDL133W</t>
+          <t>YBR139W</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YHR143W</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YKL165C</t>
+          <t>YOR328W</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YKL165C</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YBL017C</t>
+          <t>YFL011W</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YJR137C</t>
+          <t>YNR002C</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YIL166C</t>
+          <t>YMR155W</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YLR042C</t>
+          <t>YNL129W</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YDR536W</t>
+          <t>YDR415C</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>YIR028W</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YOR383C</t>
+          <t>YMR058W</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YBR161W</t>
+          <t>YBR021W</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YEL065W</t>
+          <t>YNL019C</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>YOR099W</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YPR075C</t>
+          <t>YDL010W</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YJR152W</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YJR103W</t>
+          <t>YOR381W</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YNL101W</t>
+          <t>YER060W-A</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YJL059W</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YMR215W</t>
+          <t>YMR243C</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YIL140W</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YJL222W</t>
+          <t>YBL042C</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YKL209C</t>
+          <t>YBR014C</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YNL298W</t>
+          <t>YOR049C</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YHL047C</t>
+          <t>YJL172W</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YOR270C</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YBR162C</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YNL321W</t>
+          <t>YDL248W</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YLR043C</t>
+          <t>YHR057C</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YLR299W</t>
+          <t>YOL161C</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YKL103C</t>
+          <t>YDR422C</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YLL025W</t>
+          <t>YOL154W</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YJL219W</t>
+          <t>YGR125W</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YHL036W</t>
+          <t>YML132W</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YIL014W</t>
+          <t>YDR519W</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YBR199W</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YDL046W</t>
+          <t>YOR008C</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YHR134W</t>
+          <t>YPL163C</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YJL178C</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YJL222W</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YOL105C</t>
+          <t>YMR319C</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YPL156C</t>
+          <t>YML066C</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YPR157W</t>
+          <t>YOL101C</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YPL123C</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YOL122C</t>
+          <t>YOR382W</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>YDR281C</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YGR209C</t>
+          <t>YJL097W</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YER119C</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YLR443W</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YHR143W</t>
+          <t>YBR161W</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YNL115C</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YCR007C</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YOL101C</t>
+          <t>YFL040W</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YMR319C</t>
+          <t>YJL174W</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YOR192C</t>
+          <t>YHL008C</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YPL234C</t>
+          <t>YNL176C</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YPL265W</t>
+          <t>YLR110C</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YOR381W</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YPR037C</t>
+          <t>YNR061C</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YIR041W</t>
+          <t>YGR254W</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YBR162C</t>
+          <t>YNL012W</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YOL161C</t>
+          <t>YNL058C</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YGR209C</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YLR300W</t>
+          <t>YJR152W</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YMR251W-A</t>
+          <t>YER011W</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YKR044W</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YBL039C</t>
+          <t>YIL011W</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YPL221W</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YIL140W</t>
+          <t>YOR010C</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YNL101W</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YOR034C</t>
+          <t>YBL039C</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YNR066C</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YOL019W</t>
+          <t>YPL176C</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YIL014W</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>YIR019C</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>YNR072W</t>
+          <t>YJL079C</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>YNR076W</t>
+          <t>YNL217W</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>YDR144C</t>
+          <t>YOL132W</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>YGR279C</t>
+          <t>YNL283C</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>YLL048C</t>
+          <t>YDR438W</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YOR010C</t>
+          <t>YHR215W</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YJR001W</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>YNL283C</t>
+          <t>YDL180W</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YLR299W</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YGR223C</t>
+          <t>YHR126C</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YNL238W</t>
+          <t>YBR205W</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YGR055W</t>
+          <t>YNL318C</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YNL015W</t>
+          <t>YBR290W</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>YKL096W</t>
+          <t>YDR452W</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YJR054W</t>
+          <t>YHL036W</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YDR542W</t>
+          <t>YCR075C</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YIR019C</t>
+          <t>YPR194C</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YGR295C</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YDR497C</t>
+          <t>YNR055C</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>YJL219W</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>YBR014C</t>
+          <t>YHR132C</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YLR042C</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YOR288C</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YLR396C</t>
+          <t>YDR542W</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>YOL154W</t>
+          <t>YHR134W</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YPR194C</t>
+          <t>YDR382W</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YNL012W</t>
+          <t>YDL130W</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YDL077C</t>
+          <t>YNL298W</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YDL128W</t>
+          <t>YLL051C</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>YCR011C</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YCR069W</t>
+          <t>YIL089W</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YGR282C</t>
+          <t>YJL037W</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>YGR197C</t>
+          <t>YDR055W</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>YIL173W</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>YIR028W</t>
+          <t>YLL048C</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YJL158C</t>
+          <t>YLR043C</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>YHL048W</t>
+          <t>YNL320W</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YDR248C</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YCR069W</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YLR213C</t>
+          <t>YHL048W</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>YNL065W</t>
+          <t>YOR301W</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>YGL032C</t>
+          <t>YNL015W</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>YBR302C</t>
+          <t>YEL065W</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>YNL322C</t>
+          <t>YLR300W</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>YPL221W</t>
+          <t>YIL099W</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>YOR190W</t>
+          <t>YOL002C</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YIR041W</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>YBL042C</t>
+          <t>YDR003W</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YJR161C</t>
+          <t>YOL011W</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YML132W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YBR199W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YNR076W</t>
+          <t>YDR281C</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YPL156C</t>
+          <t>YLR042C</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YDR497C</t>
+          <t>YFL062W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YOR247W</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YDR536W</t>
+          <t>YML104C</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YOL084W</t>
+          <t>YPR026W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YGL027C</t>
+          <t>YIL162W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YIL158W</t>
+          <t>YPL221W</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YPR037C</t>
+          <t>YNL217W</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YPL234C</t>
+          <t>YNL320W</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YJR004C</t>
+          <t>YLR461W</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YKL196C</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YJR161C</t>
+          <t>YJR040W</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YDR536W</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YNL279W</t>
+          <t>YKR044W</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YHL047C</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YKL124W</t>
+          <t>YKL096W</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YML012W</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>YPL156C</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YHL040C</t>
+          <t>YDL130W</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YDR040C</t>
+          <t>YIR041W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>YBR036C</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YOL103W</t>
+          <t>YNR072W</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YOR383C</t>
+          <t>YDR519W</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YDL046W</t>
+          <t>YJL037W</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YHR174W</t>
+          <t>YDL049C</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YGL186C</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>YHL042W</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>YKL224C</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YKL220C</t>
+          <t>YOR270C</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YGR223C</t>
+          <t>YOR288C</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YML123C</t>
+          <t>YGR260W</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>YGR279C</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YNL322C</t>
+          <t>YKL103C</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YOR192C</t>
+          <t>YOL002C</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YJR137C</t>
+          <t>YDR542W</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YGR197C</t>
+          <t>YOR292C</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YGL089C</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YKL096W</t>
+          <t>YLR110C</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YGR279C</t>
+          <t>YOL138C</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YOR214C</t>
+          <t>YBR302C</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YJL222W</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YOR010C</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YKL034W</t>
+          <t>YNL012W</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YBR139W</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YNR028W</t>
+          <t>YPL176C</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YKL146W</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YJL051W</t>
+          <t>YLR443W</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YBR286W</t>
+          <t>YHR057C</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YIL166C</t>
+          <t>YLR299W</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YCR028C</t>
+          <t>YOR008C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>YGR197C</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YJL219W</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YHL040C</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YOR034C</t>
+          <t>YMR058W</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YHL047C</t>
+          <t>YMR251W-A</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YHR151C</t>
+          <t>YOR034C</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YPL265W</t>
+          <t>YJL158C</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YHL008C</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YGL186C</t>
+          <t>YIL011W</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YLR250W</t>
+          <t>YOL154W</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YOR190W</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YDL049C</t>
+          <t>YJL172W</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YOL158C</t>
+          <t>YBL042C</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YGR055W</t>
+          <t>YCR011C</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YLL025W</t>
+          <t>YDR262W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YNR028W</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YLR037C</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YLR104W</t>
+          <t>YLR250W</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YKL220C</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YER119C</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YLR286C</t>
+          <t>YJL178C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>YMR244W</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YPR075C</t>
+          <t>YER123W</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>YOL007C</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YLR361C</t>
+          <t>YOL158C</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YML047C</t>
+          <t>YLR043C</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YOL019W</t>
+          <t>YDR452W</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YJL160C</t>
+          <t>YPL234C</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YPR026W</t>
+          <t>YHR174W</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YFL020C</t>
+          <t>YOR087W</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YJL223C</t>
+          <t>YDL180W</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YKL146W</t>
+          <t>YJL174W</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YBR036C</t>
+          <t>YKL209C</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YNL327W</t>
+          <t>YEL060C</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YGR282C</t>
+          <t>YMR011W</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YKL209C</t>
+          <t>YNL279W</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YLR213C</t>
+          <t>YGR223C</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YML104C</t>
+          <t>YGR125W</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YBL017C</t>
+          <t>YIL166C</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YPL057C</t>
+          <t>YOR049C</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YGL027C</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YOL138C</t>
+          <t>YIR028W</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YMR251W-A</t>
+          <t>YOR382W</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YIL173W</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YML001W</t>
+          <t>YBR014C</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YDL077C</t>
+          <t>YIL099W</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YEL060C</t>
+          <t>YHL036W</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YGL032C</t>
+          <t>YBR290W</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YLR343W</t>
+          <t>YGR055W</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YBR187W</t>
+          <t>YHR202W</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YER011W</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YJR103W</t>
+          <t>YKR093W</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YKL224C</t>
+          <t>YLR343W</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YMR215W</t>
+          <t>YNL283C</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>YOR381W</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YLR220W</t>
+          <t>YPL053C</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YNR072W</t>
+          <t>YDR497C</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YJR040W</t>
+          <t>YEL065W</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YBR040W</t>
+          <t>YDL046W</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YPL053C</t>
+          <t>YKL034W</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YBR302C</t>
+          <t>YNL176C</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YNL238W</t>
+          <t>YLR332W</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YLR461W</t>
+          <t>YDL077C</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YMR319C</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YGL203C</t>
+          <t>YHR132C</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YDL128W</t>
+          <t>YNL305C</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YER123W</t>
+          <t>YOL019W</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YOR009W</t>
+          <t>YKR013W</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YLR413W</t>
+          <t>YBR162C</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YKL217W</t>
+          <t>YMR215W</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YML066C</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YPR157W</t>
+          <t>YIL067C</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YDR144C</t>
+          <t>YPR037C</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YLR194C</t>
+          <t>YJR160C</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YJR160C</t>
+          <t>YDL133W</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YLR037C</t>
+          <t>YKL165C</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YNL065W</t>
+          <t>YBR187W</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YLR332W</t>
+          <t>YHR126C</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YCR098C</t>
+          <t>YJL160C</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YML012W</t>
+          <t>YKL217W</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YNL321W</t>
+          <t>YJR103W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YCL001W</t>
+          <t>YOL122C</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YJR054W</t>
+          <t>YNL065W</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>YJL132W</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YDL133W</t>
+          <t>YER060W-A</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YNL275W</t>
+          <t>YML047C</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YLR396C</t>
+          <t>YBL017C</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YKL103C</t>
+          <t>YGR254W</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YGL263W</t>
+          <t>YFL020C</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YCR069W</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YJL158C</t>
+          <t>YOR383C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YOL105C</t>
+          <t>YOL011W</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YNL321W</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YOL122C</t>
+          <t>YDR003W</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YKR013W</t>
+          <t>YDR382W</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YKR093W</t>
+          <t>YHR134W</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YBR139W</t>
+          <t>YLL025W</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YHR143W</t>
+          <t>YPL123C</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YOR328W</t>
+          <t>YHR173C</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YKL165C</t>
+          <t>YPL154C</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YLL043W</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YNR002C</t>
+          <t>YDL128W</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YNL326C</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YNL129W</t>
+          <t>YJL079C</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>YIL140W</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YIR028W</t>
+          <t>YNL129W</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YMR058W</t>
+          <t>YJR152W</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YBR021W</t>
+          <t>YJR137C</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>YOR214C</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YOR099W</t>
+          <t>YBR021W</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YDL010W</t>
+          <t>YLR213C</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YIL014W</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YBR161W</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YOR381W</t>
+          <t>YPL057C</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YER060W-A</t>
+          <t>YPR157W</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YNL275W</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YMR243C</t>
+          <t>YOR301W</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YIL140W</t>
+          <t>YHR151C</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YBL042C</t>
+          <t>YDR438W</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YBR014C</t>
+          <t>YJR054W</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YOR049C</t>
+          <t>YLR286C</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YJL172W</t>
+          <t>YNL318C</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YOR270C</t>
+          <t>YDR144C</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YBR162C</t>
+          <t>YML123C</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YGL203C</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YHR057C</t>
+          <t>YNR076W</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YOL161C</t>
+          <t>YCR098C</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YDR422C</t>
+          <t>YDR415C</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YOL154W</t>
+          <t>YDR422C</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YGL089C</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YGR282C</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YDR519W</t>
+          <t>YOL105C</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YBR199W</t>
+          <t>YPR075C</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YOR008C</t>
+          <t>YOR247W</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YPL163C</t>
+          <t>YDL211C</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YOR009W</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YJL222W</t>
+          <t>YPL265W</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YMR319C</t>
+          <t>YLR046C</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YML066C</t>
+          <t>YOL161C</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YOL101C</t>
+          <t>YNL058C</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YPL123C</t>
+          <t>YDR055W</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YOR382W</t>
+          <t>YOR192C</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YBL039C</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YER119C</t>
+          <t>YNR002C</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YLR443W</t>
+          <t>YNR055C</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YBR161W</t>
+          <t>YML001W</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>YIL158W</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>YCR007C</t>
+          <t>YLR001C</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>YJR161C</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YJL174W</t>
+          <t>YJL116C</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>YJL051W</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YNL019C</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YLR110C</t>
+          <t>YDR040C</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YLL048C</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YLR220W</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YGR254W</t>
+          <t>YLR194C</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YNL012W</t>
+          <t>YIL088C</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YGR209C</t>
+          <t>YOR099W</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YJR152W</t>
+          <t>YNR066C</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YMR011W</t>
+          <t>YLL051C</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YER011W</t>
+          <t>YDR248C</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YKR044W</t>
+          <t>YBR286W</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YIL011W</t>
+          <t>YHR143W</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>YPL221W</t>
+          <t>YNL298W</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YOR010C</t>
+          <t>YGL032C</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YNL101W</t>
+          <t>YMR297W</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YBL039C</t>
+          <t>YGR295C</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YNL015W</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YMR155W</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YIL014W</t>
+          <t>YGL263W</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YIR019C</t>
+          <t>YNL336W</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>YJL079C</t>
+          <t>YLR297W</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YNL238W</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>YOL132W</t>
+          <t>YMR243C</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>YNL283C</t>
+          <t>YOL103W</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YNL327W</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YHR215W</t>
+          <t>YLR396C</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YHL048W</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>YDL180W</t>
+          <t>YCR007C</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>YLR299W</t>
+          <t>YNL115C</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YHR126C</t>
+          <t>YGR209C</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YBR205W</t>
+          <t>YOL132W</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YNR061C</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YBR290W</t>
+          <t>YMR221C</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>YDR452W</t>
+          <t>YCL057W</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YHL036W</t>
+          <t>YJR001W</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YCR075C</t>
+          <t>YJL097W</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YPR194C</t>
+          <t>YCR075C</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YJL059W</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YNL322C</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>YJL219W</t>
+          <t>YCL001W</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>YHR132C</t>
+          <t>YJR004C</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>YLR042C</t>
+          <t>YBR040W</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>YOR288C</t>
+          <t>YBR205W</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YDR542W</t>
+          <t>YDL010W</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>YHR134W</t>
+          <t>YHR215W</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YDR382W</t>
+          <t>YKL124W</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YDL130W</t>
+          <t>YLR361C</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YNL298W</t>
+          <t>YLR413W</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YJL151C</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YCR011C</t>
+          <t>YIL089W</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>YCR028C</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YJL037W</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>YDR055W</t>
+          <t>YLR104W</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>YIL173W</t>
+          <t>YOR119C</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>YLL048C</t>
+          <t>YPR194C</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YLR043C</t>
+          <t>YFL040W</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YDL248W</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>YJL223C</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YCR069W</t>
+          <t>YOL101C</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YHL048W</t>
+          <t>YFL011W</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>YOR301W</t>
+          <t>YOR328W</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>YNL015W</t>
+          <t>YLR300W</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>YEL065W</t>
+          <t>YOL084W</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>YLR300W</t>
+          <t>YPL163C</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YIR019C</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>YOL002C</t>
+          <t>YOR190W</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YIR041W</t>
+          <t>YCR101C</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YOR316C</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YOL011W</t>
+          <t>YNL101W</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/fungal_type_vacuole_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YER060W-A</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YBR199W</t>
+          <t>YJR103W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YGR055W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YLR042C</t>
+          <t>YNL283C</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YNL015W</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YML104C</t>
+          <t>YDL128W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YPR026W</t>
+          <t>YJR137C</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YNL320W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YPL221W</t>
+          <t>YKL220C</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YJL219W</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YBL042C</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YLR461W</t>
+          <t>YML001W</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YOR383C</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YJR040W</t>
+          <t>YKL217W</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YDR536W</t>
+          <t>YGL186C</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YKR044W</t>
+          <t>YBR161W</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YHL047C</t>
+          <t>YJL079C</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YKL096W</t>
+          <t>YDR415C</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YML012W</t>
+          <t>YIL140W</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YPL156C</t>
+          <t>YHL042W</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YDL130W</t>
+          <t>YLL048C</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YIR041W</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YBR036C</t>
+          <t>YPR157W</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YNR072W</t>
+          <t>YJL160C</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YDR519W</t>
+          <t>YLL025W</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YJL037W</t>
+          <t>YDR281C</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YDL049C</t>
+          <t>YIL173W</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YGL186C</t>
+          <t>YJL132W</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>YHR215W</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YKL224C</t>
+          <t>YDR438W</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YOR270C</t>
+          <t>YIL089W</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YOR288C</t>
+          <t>YEL060C</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YMR058W</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YGR279C</t>
+          <t>YOL101C</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YKL103C</t>
+          <t>YPL221W</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YOL002C</t>
+          <t>YCL057W</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YDR542W</t>
+          <t>YHR143W</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YJL223C</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YKL103C</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YLR110C</t>
+          <t>YLR037C</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YOL138C</t>
+          <t>YOR099W</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YBR302C</t>
+          <t>YOR008C</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YJL222W</t>
+          <t>YOL161C</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YOR010C</t>
+          <t>YPR026W</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YNL012W</t>
+          <t>YNL238W</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YBR139W</t>
+          <t>YDL010W</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YPL282C</t>
+          <t>YLR413W</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YDR542W</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YKL146W</t>
+          <t>YNL129W</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YLR443W</t>
+          <t>YLR001C</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YHR057C</t>
+          <t>YNR066C</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YLR299W</t>
+          <t>YOL007C</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YOR008C</t>
+          <t>YOR010C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YGR197C</t>
+          <t>YNR061C</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YJL219W</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YHL040C</t>
+          <t>YKL124W</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YMR058W</t>
+          <t>YHR151C</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YMR251W-A</t>
+          <t>YNR072W</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YOR034C</t>
+          <t>YGR197C</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YJL158C</t>
+          <t>YNL065W</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>YER119C</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YIL011W</t>
+          <t>YJR001W</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YOL154W</t>
+          <t>YLR300W</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YFL020C</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YBL042C</t>
+          <t>YER011W</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YCR011C</t>
+          <t>YNL326C</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YDR452W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YNR028W</t>
+          <t>YOR192C</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YLR037C</t>
+          <t>YOL103W</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YLR250W</t>
+          <t>YOR382W</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YKL220C</t>
+          <t>YLR104W</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YER119C</t>
+          <t>YKL196C</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YJL116C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>YCR007C</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YER123W</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YHR174W</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YOL158C</t>
+          <t>YCR075C</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YLR043C</t>
+          <t>YER123W</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YDR452W</t>
+          <t>YIR028W</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YPL234C</t>
+          <t>YOR087W</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YHR174W</t>
+          <t>YGL032C</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YPL176C</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YDL180W</t>
+          <t>YPL282C</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YJL174W</t>
+          <t>YDR536W</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YKL209C</t>
+          <t>YJL158C</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YEL060C</t>
+          <t>YLR220W</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YMR011W</t>
+          <t>YOL132W</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YNL279W</t>
+          <t>YOL011W</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YGR223C</t>
+          <t>YOL138C</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YOR247W</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YIL166C</t>
+          <t>YCR028C</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YOR049C</t>
+          <t>YIL166C</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YGL027C</t>
+          <t>YOR328W</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YIR028W</t>
+          <t>YGL203C</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YOR382W</t>
+          <t>YCR069W</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YIL173W</t>
+          <t>YHR057C</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YBR014C</t>
+          <t>YCR098C</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YHR132C</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YHL036W</t>
+          <t>YBR139W</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YBR290W</t>
+          <t>YKL096W</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YGR055W</t>
+          <t>YBL039C</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YBR014C</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YER011W</t>
+          <t>YJL151C</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YKR093W</t>
+          <t>YNL058C</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YLR343W</t>
+          <t>YPL234C</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YNL283C</t>
+          <t>YLR042C</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YOR381W</t>
+          <t>YDL133W</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YPL053C</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YDR497C</t>
+          <t>YNL321W</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YEL065W</t>
+          <t>YDR003W</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YDL046W</t>
+          <t>YCL001W</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YKL034W</t>
+          <t>YHR173C</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YHL008C</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YLR332W</t>
+          <t>YHL040C</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YDL077C</t>
+          <t>YIL158W</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YMR319C</t>
+          <t>YJR152W</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YHR132C</t>
+          <t>YLR361C</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YGR125W</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YOL019W</t>
+          <t>YBR187W</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YKR013W</t>
+          <t>YIL099W</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YBR162C</t>
+          <t>YKL146W</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YMR215W</t>
+          <t>YDL130W</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YML066C</t>
+          <t>YJR040W</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>YJR160C</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YPR037C</t>
+          <t>YGR295C</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YJR160C</t>
+          <t>YNL101W</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YDL133W</t>
+          <t>YOL019W</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YKL165C</t>
+          <t>YGL089C</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YBR187W</t>
+          <t>YIR041W</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YHR126C</t>
+          <t>YNL217W</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YJL160C</t>
+          <t>YDR262W</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YKL217W</t>
+          <t>YJL174W</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YJR103W</t>
+          <t>YMR215W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YOL122C</t>
+          <t>YLR046C</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YNL065W</t>
+          <t>YNL012W</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>YLR299W</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YER060W-A</t>
+          <t>YIR019C</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YML047C</t>
+          <t>YNL115C</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YBL017C</t>
+          <t>YDR040C</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YGR254W</t>
+          <t>YOR316C</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YFL020C</t>
+          <t>YPL163C</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YCR069W</t>
+          <t>YLR443W</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YOR383C</t>
+          <t>YPL123C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YOL011W</t>
+          <t>YHR134W</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YNL321W</t>
+          <t>YPR194C</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YNR055C</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YDR382W</t>
+          <t>YPL154C</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YHR134W</t>
+          <t>YBL017C</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YLL025W</t>
+          <t>YJL037W</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YPL123C</t>
+          <t>YLL043W</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>YML066C</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YOR292C</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YPR037C</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YDL128W</t>
+          <t>YDR422C</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YLR194C</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YJL079C</t>
+          <t>YLR043C</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YIL140W</t>
+          <t>YLL051C</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YNL129W</t>
+          <t>YNL318C</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YJR152W</t>
+          <t>YEL065W</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YJR137C</t>
+          <t>YIL014W</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YOR214C</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YBR021W</t>
+          <t>YOL154W</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YLR213C</t>
+          <t>YDL046W</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YIL014W</t>
+          <t>YKL165C</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YBR161W</t>
+          <t>YGR254W</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YPL057C</t>
+          <t>YML123C</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YPR157W</t>
+          <t>YJL178C</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YNL275W</t>
+          <t>YHL048W</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YOR301W</t>
+          <t>YKL224C</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YHR151C</t>
+          <t>YLR250W</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YML132W</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YJR054W</t>
+          <t>YMR221C</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YLR286C</t>
+          <t>YNL336W</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YOR009W</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YDR144C</t>
+          <t>YMR244W</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YML123C</t>
+          <t>YIL067C</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YGL203C</t>
+          <t>YKL034W</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YNR076W</t>
+          <t>YJL059W</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YCR098C</t>
+          <t>YHL036W</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>YJR004C</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YDR422C</t>
+          <t>YMR319C</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YGL089C</t>
+          <t>YOL105C</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YGR282C</t>
+          <t>YMR243C</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YOL105C</t>
+          <t>YPL265W</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YPR075C</t>
+          <t>YNL327W</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YOR247W</t>
+          <t>YHR126C</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>YBR199W</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YOR009W</t>
+          <t>YLR213C</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YPL265W</t>
+          <t>YKL209C</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>YPR075C</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YOL161C</t>
+          <t>YBR302C</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YCR011C</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YDR055W</t>
+          <t>YIL088C</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YOR192C</t>
+          <t>YMR251W-A</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YOR034C</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YBL039C</t>
+          <t>YBR036C</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YNR002C</t>
+          <t>YLR286C</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YOR381W</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YML001W</t>
+          <t>YNR076W</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YIL158W</t>
+          <t>YDR519W</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YBR040W</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YJR161C</t>
+          <t>YJL097W</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YLR461W</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YJL051W</t>
+          <t>YNL019C</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>YPL156C</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YDR040C</t>
+          <t>YMR155W</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YLL048C</t>
+          <t>YBR021W</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YLR220W</t>
+          <t>YDL211C</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YLR194C</t>
+          <t>YPL057C</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YLR343W</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YDR382W</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YOR099W</t>
+          <t>YOR301W</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YNL322C</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YOR190W</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>YDL248W</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YBR286W</t>
+          <t>YKR044W</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YHR143W</t>
+          <t>YML104C</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>YNL298W</t>
+          <t>YPL053C</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YGL032C</t>
+          <t>YJL051W</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YGR223C</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YML012W</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YNL015W</t>
+          <t>YJL222W</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YNL305C</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YGL263W</t>
+          <t>YDR497C</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YDL180W</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>YGL263W</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>YNL238W</t>
+          <t>YGR260W</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>YMR243C</t>
+          <t>YJR161C</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>YOL103W</t>
+          <t>YNR002C</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>YNL327W</t>
+          <t>YGR209C</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YLR396C</t>
+          <t>YLR332W</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>YHL048W</t>
+          <t>YBR290W</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>YCR007C</t>
+          <t>YFL011W</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>YIL162W</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YGR209C</t>
+          <t>YJR054W</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YOL132W</t>
+          <t>YNL279W</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YOR270C</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YBR162C</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YLR110C</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YOL084W</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YFL062W</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YCR075C</t>
+          <t>YLR297W</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YOR214C</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YNL322C</t>
+          <t>YDR144C</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>YCL001W</t>
+          <t>YOR288C</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>YJR004C</t>
+          <t>YFL040W</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>YBR040W</t>
+          <t>YLR396C</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>YBR205W</t>
+          <t>YNL176C</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YDL010W</t>
+          <t>YOL122C</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>YHR215W</t>
+          <t>YNL298W</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YKL124W</t>
+          <t>YDR248C</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YLR361C</t>
+          <t>YML047C</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YLR413W</t>
+          <t>YHL047C</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YKR093W</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>YOR049C</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YCR028C</t>
+          <t>YDL049C</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>YDR055W</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>YLR104W</t>
+          <t>YNL275W</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YGL027C</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>YPR194C</t>
+          <t>YKR013W</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>YCR101C</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YIL011W</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>YJL223C</t>
+          <t>YBR286W</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YOL101C</t>
+          <t>YOR119C</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YOL158C</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>YOR328W</t>
+          <t>YHR202W</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>YLR300W</t>
+          <t>YOL002C</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>YOL084W</t>
+          <t>YMR297W</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>YPL163C</t>
+          <t>YBR205W</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>YIR019C</t>
+          <t>YGR282C</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>YOR190W</t>
+          <t>YNR028W</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>YGR279C</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YDL077C</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YNL101W</t>
+          <t>YMR011W</t>
         </is>
       </c>
     </row>
